--- a/5/search/FY2_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile2_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278.2</v>
+        <v>292.8</v>
       </c>
       <c r="C3" t="n">
-        <v>139.5</v>
+        <v>127.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4.000000000000001</v>
+        <v>4.000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY2_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile2_results/fine_tuned/comparison.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="C2" t="n">
         <v>140</v>
@@ -476,10 +476,10 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>292.8</v>
+        <v>262.3</v>
       </c>
       <c r="C3" t="n">
-        <v>127.6</v>
+        <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>4.000000000000002</v>
